--- a/Pasta1 30 MARÇO.xlsx
+++ b/Pasta1 30 MARÇO.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aluno.GR-D-DL-13.000\Documents\GitHub\AnaRaquel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1F4F2983-6628-4A63-81B5-506C22B3B8AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{695F094A-7271-4A82-9741-48D8A4163600}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="15225" yWindow="1245" windowWidth="13290" windowHeight="13440" xr2:uid="{D472D033-26B5-4FFE-AA7A-9D4B89486CD9}"/>
+    <workbookView xWindow="13230" yWindow="0" windowWidth="13290" windowHeight="15585" xr2:uid="{D472D033-26B5-4FFE-AA7A-9D4B89486CD9}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -603,6 +603,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="9">
+        <f>WORKDAY.INTL(B8-1,1,1,)</f>
         <v>46111</v>
       </c>
       <c r="B11" s="10">
@@ -624,6 +625,7 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="9">
+        <f>WORKDAY.INTL(A11,1,1,)</f>
         <v>46112</v>
       </c>
       <c r="B12" s="10">
@@ -646,13 +648,14 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="9">
+        <f t="shared" ref="A13:A34" si="1">WORKDAY.INTL(A12,1,1,)</f>
         <v>46113</v>
       </c>
       <c r="B13" s="10">
         <v>46113</v>
       </c>
       <c r="C13" s="3">
-        <f t="shared" ref="C13:C34" si="1">F12</f>
+        <f t="shared" ref="C13:C34" si="2">F12</f>
         <v>0</v>
       </c>
       <c r="D13" s="3">
@@ -668,13 +671,14 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="9">
+        <f t="shared" si="1"/>
         <v>46114</v>
       </c>
       <c r="B14" s="10">
         <v>46114</v>
       </c>
       <c r="C14" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="D14" s="3">
@@ -690,13 +694,14 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="9">
+        <f t="shared" si="1"/>
         <v>46115</v>
       </c>
       <c r="B15" s="10">
         <v>46115</v>
       </c>
       <c r="C15" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>5</v>
       </c>
       <c r="D15" s="3">
@@ -712,13 +717,14 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="9">
+        <f t="shared" si="1"/>
         <v>46118</v>
       </c>
       <c r="B16" s="10">
         <v>46118</v>
       </c>
       <c r="C16" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>8</v>
       </c>
       <c r="D16" s="3">
@@ -734,13 +740,14 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="9">
+        <f t="shared" si="1"/>
         <v>46119</v>
       </c>
       <c r="B17" s="10">
         <v>46119</v>
       </c>
       <c r="C17" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>10</v>
       </c>
       <c r="D17" s="3">
@@ -756,13 +763,14 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="9">
+        <f t="shared" si="1"/>
         <v>46120</v>
       </c>
       <c r="B18" s="10">
         <v>46120</v>
       </c>
       <c r="C18" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>18</v>
       </c>
       <c r="D18" s="3">
@@ -778,13 +786,14 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="9">
+        <f t="shared" si="1"/>
         <v>46121</v>
       </c>
       <c r="B19" s="10">
         <v>46121</v>
       </c>
       <c r="C19" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>5</v>
       </c>
       <c r="D19" s="3">
@@ -800,13 +809,14 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="9">
+        <f t="shared" si="1"/>
         <v>46122</v>
       </c>
       <c r="B20" s="10">
         <v>46122</v>
       </c>
       <c r="C20" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="D20" s="3">
@@ -822,13 +832,14 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="9">
+        <f t="shared" si="1"/>
         <v>46125</v>
       </c>
       <c r="B21" s="10">
         <v>46125</v>
       </c>
       <c r="C21" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>6</v>
       </c>
       <c r="D21" s="3">
@@ -844,13 +855,14 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="9">
+        <f t="shared" si="1"/>
         <v>46126</v>
       </c>
       <c r="B22" s="10">
         <v>46126</v>
       </c>
       <c r="C22" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>3</v>
       </c>
       <c r="D22" s="3">
@@ -866,13 +878,14 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="9">
+        <f t="shared" si="1"/>
         <v>46127</v>
       </c>
       <c r="B23" s="10">
         <v>46127</v>
       </c>
       <c r="C23" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>9</v>
       </c>
       <c r="D23" s="3">
@@ -888,13 +901,14 @@
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="9">
+        <f t="shared" si="1"/>
         <v>46128</v>
       </c>
       <c r="B24" s="10">
         <v>46128</v>
       </c>
       <c r="C24" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>14</v>
       </c>
       <c r="D24" s="3">
@@ -910,13 +924,14 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="9">
+        <f t="shared" si="1"/>
         <v>46129</v>
       </c>
       <c r="B25" s="10">
         <v>46129</v>
       </c>
       <c r="C25" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="D25" s="3">
@@ -932,13 +947,14 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="9">
+        <f t="shared" si="1"/>
         <v>46132</v>
       </c>
       <c r="B26" s="10">
         <v>46132</v>
       </c>
       <c r="C26" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>11</v>
       </c>
       <c r="D26" s="3">
@@ -954,13 +970,14 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="9">
+        <f t="shared" si="1"/>
         <v>46133</v>
       </c>
       <c r="B27" s="10">
         <v>46133</v>
       </c>
       <c r="C27" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>8</v>
       </c>
       <c r="D27" s="3">
@@ -976,13 +993,14 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="9">
+        <f t="shared" si="1"/>
         <v>46134</v>
       </c>
       <c r="B28" s="10">
         <v>46134</v>
       </c>
       <c r="C28" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>5</v>
       </c>
       <c r="D28" s="3">
@@ -998,13 +1016,14 @@
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="9">
+        <f t="shared" si="1"/>
         <v>46135</v>
       </c>
       <c r="B29" s="10">
         <v>46135</v>
       </c>
       <c r="C29" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="D29" s="3">
@@ -1020,13 +1039,14 @@
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="9">
+        <f t="shared" si="1"/>
         <v>46136</v>
       </c>
       <c r="B30" s="10">
         <v>46136</v>
       </c>
       <c r="C30" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>7</v>
       </c>
       <c r="D30" s="3">
@@ -1042,13 +1062,14 @@
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="9">
+        <f t="shared" si="1"/>
         <v>46139</v>
       </c>
       <c r="B31" s="10">
         <v>46139</v>
       </c>
       <c r="C31" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>5</v>
       </c>
       <c r="D31" s="3">
@@ -1064,13 +1085,14 @@
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="9">
+        <f t="shared" si="1"/>
         <v>46140</v>
       </c>
       <c r="B32" s="10">
         <v>46140</v>
       </c>
       <c r="C32" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>15</v>
       </c>
       <c r="D32" s="3">
@@ -1086,13 +1108,14 @@
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="9">
+        <f t="shared" si="1"/>
         <v>46141</v>
       </c>
       <c r="B33" s="10">
         <v>46141</v>
       </c>
       <c r="C33" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>15</v>
       </c>
       <c r="D33" s="3">
@@ -1108,13 +1131,14 @@
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="9">
+        <f t="shared" si="1"/>
         <v>46142</v>
       </c>
       <c r="B34" s="10">
         <v>46142</v>
       </c>
       <c r="C34" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>15</v>
       </c>
       <c r="D34" s="3">
